--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>allegato DDT 27-04-2026</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>allegato DDT 27-04-2026</t>
         </is>
       </c>
     </row>
@@ -1410,6 +1410,262 @@
       <c r="C66" t="inlineStr">
         <is>
           <t>allegato DDT 23-04-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>p8831</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>p8767</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>p13947</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>p2301</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>p1950</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>p2357</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>p1704</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>p2355</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="n"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>p1792</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="n"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>p2356</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>p1794</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>p6525</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>p8847</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>p2254</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>p1861</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>p2353</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>p2354</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>p1793</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>p13495</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>p2302</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>p1951</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
         </is>
       </c>
     </row>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1419,6 +1419,9 @@
           <t>p8831</t>
         </is>
       </c>
+      <c r="B67" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1431,6 +1434,9 @@
           <t>p8767</t>
         </is>
       </c>
+      <c r="B68" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1443,6 +1449,9 @@
           <t>p13947</t>
         </is>
       </c>
+      <c r="B69" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1455,6 +1464,9 @@
           <t>p2301</t>
         </is>
       </c>
+      <c r="B70" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1467,6 +1479,9 @@
           <t>p1950</t>
         </is>
       </c>
+      <c r="B71" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1479,6 +1494,9 @@
           <t>p2357</t>
         </is>
       </c>
+      <c r="B72" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1491,6 +1509,9 @@
           <t>p1704</t>
         </is>
       </c>
+      <c r="B73" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1503,7 +1524,9 @@
           <t>p2355</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n"/>
+      <c r="B74" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1516,7 +1539,9 @@
           <t>p1792</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n"/>
+      <c r="B75" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1529,6 +1554,9 @@
           <t>p2356</t>
         </is>
       </c>
+      <c r="B76" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1541,6 +1569,9 @@
           <t>p1794</t>
         </is>
       </c>
+      <c r="B77" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1553,7 +1584,9 @@
           <t>p6525</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n"/>
+      <c r="B78" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1566,7 +1599,9 @@
           <t>p8847</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n"/>
+      <c r="B79" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1579,6 +1614,9 @@
           <t>p2254</t>
         </is>
       </c>
+      <c r="B80" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1591,6 +1629,9 @@
           <t>p1861</t>
         </is>
       </c>
+      <c r="B81" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1603,6 +1644,9 @@
           <t>p2353</t>
         </is>
       </c>
+      <c r="B82" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1615,6 +1659,9 @@
           <t>p2354</t>
         </is>
       </c>
+      <c r="B83" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1627,6 +1674,9 @@
           <t>p1793</t>
         </is>
       </c>
+      <c r="B84" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1639,6 +1689,9 @@
           <t>p13495</t>
         </is>
       </c>
+      <c r="B85" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1651,6 +1704,9 @@
           <t>p2302</t>
         </is>
       </c>
+      <c r="B86" s="1" t="n">
+        <v>46135</v>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>in lavorazione</t>
@@ -1662,6 +1718,9 @@
         <is>
           <t>p1951</t>
         </is>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>46135</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1728,6 +1728,36 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>p1704</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>allegato DDT 30-04-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>p1951</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 30-04-2026</t>
         </is>
       </c>
     </row>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>allegato DDT 30-04-2026</t>
+          <t>In lavorazione</t>
         </is>
       </c>
     </row>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>in lavorazione</t>
         </is>
       </c>
     </row>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1754,9 +1754,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
-        </is>
-      </c>
+          <t>allegato DDT 30-04-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>p2100</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1767,7 +1767,14 @@
       <c r="B90" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Foglio1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1774,9 +1775,351 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="1" t="n"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>p1736</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>p1752</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>p1754</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>p1755</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>p1759</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>p1761</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>p1762</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>p1764</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>p1765</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>p1766</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>p1788</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>p1808</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>p1816</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>p1831</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>p1892</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>p1902</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>04/05/2026_2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>p2176</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>p1788</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>p13474</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>p2428</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -414,11 +414,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="17.81640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.81640625" customWidth="1" min="2" max="2"/>
     <col width="31.81640625" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1785,11 +1785,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1802,11 +1798,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1819,11 +1811,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1836,11 +1824,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1853,11 +1837,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1870,11 +1850,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1887,11 +1863,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1904,11 +1876,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1921,11 +1889,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1938,11 +1902,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1957,7 +1917,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>in lavorazione</t>
         </is>
       </c>
     </row>
@@ -1972,11 +1932,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1989,11 +1945,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2008,7 +1960,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>in lavorazione</t>
         </is>
       </c>
     </row>
@@ -2023,11 +1975,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2040,11 +1988,7 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2055,11 +1999,7 @@
       <c r="B107" s="1" t="n">
         <v>46090</v>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2072,7 +2012,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>in lavorazione</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2027,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>In lavorazione</t>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>mancano 30 porzioni di mousse</t>
         </is>
       </c>
     </row>
@@ -2100,11 +2045,237 @@
       <c r="B110" s="1" t="n">
         <v>46135</v>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>mancano 40 porzioni di mousse</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>p2025</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS13695</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>p2286</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51851</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>p2271</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51848</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>p9804</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS52172</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>p1760</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS13653</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>p2154</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51831</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>p1948</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS13685</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>p11119</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS52193</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>p2270</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51847</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>p2269</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51846</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>p2293</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51852</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>p2273</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51850</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>p2272</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51849</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>p2330</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS51857</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>p1919</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS13674</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>p1778</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS13658</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>p2658</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>05-05-2026_FNS13704</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 06-05-2026</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 06-05-2026</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,11 @@
       <c r="B107" s="1" t="n">
         <v>46090</v>
       </c>
-      <c r="C107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2012,7 +2016,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 06-05-2026</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2031,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 06-05-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2045,7 +2049,11 @@
       <c r="B110" s="1" t="n">
         <v>46135</v>
       </c>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>mancano 40 porzioni di mousse</t>
@@ -2063,7 +2071,11 @@
           <t>05-05-2026_FNS13695</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2076,7 +2088,11 @@
           <t>05-05-2026_FNS51851</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2089,7 +2105,11 @@
           <t>05-05-2026_FNS51848</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2102,7 +2122,11 @@
           <t>05-05-2026_FNS52172</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2115,7 +2139,11 @@
           <t>05-05-2026_FNS13653</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2128,7 +2156,11 @@
           <t>05-05-2026_FNS51831</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2143,7 +2175,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 06-05-2026</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2190,11 @@
           <t>05-05-2026_FNS52193</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2171,7 +2207,11 @@
           <t>05-05-2026_FNS51847</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2184,7 +2224,11 @@
           <t>05-05-2026_FNS51846</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2197,7 +2241,11 @@
           <t>05-05-2026_FNS51852</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2210,7 +2258,11 @@
           <t>05-05-2026_FNS51850</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2223,7 +2275,11 @@
           <t>05-05-2026_FNS51849</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2236,7 +2292,11 @@
           <t>05-05-2026_FNS51857</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2249,7 +2309,11 @@
           <t>05-05-2026_FNS13674</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2262,7 +2326,11 @@
           <t>05-05-2026_FNS13658</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2275,7 +2343,11 @@
           <t>05-05-2026_FNS13704</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>allegato DDT 06-05-2027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1785,7 +1785,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1798,7 +1802,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1811,7 +1819,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1824,7 +1836,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1837,7 +1853,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1850,7 +1870,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1863,7 +1887,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1876,7 +1904,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1889,7 +1921,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1902,7 +1938,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1932,7 +1972,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1945,7 +1989,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1975,7 +2023,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1988,7 +2040,11 @@
           <t>04/05/2026_2</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,19 +25,19 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +52,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -748,10 +749,9 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN53102</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>07-05-2026_FNS53102</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -761,10 +761,9 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN14260</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>07-05-2026_FNS14260</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -774,10 +773,9 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN53094</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>07-05-2026_FNS53094</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -787,10 +785,9 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN14315</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>07-05-2026_FNS14315</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -800,10 +797,9 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN53095</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>07-05-2026_FNS53095</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -813,10 +809,9 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN14314</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>07-05-2026_FNS14314</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -826,7 +821,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13369</t>
+          <t>04-05-2026_FNS13369</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -843,7 +838,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13371</t>
+          <t>04-05-2026_FNS13371</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -860,7 +855,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13370</t>
+          <t>04-05-2026_FNS13370</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13366</t>
+          <t>04-05-2026_FNS13366</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13367</t>
+          <t>04-05-2026_FNS13367</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -911,10 +906,9 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07-05-2026_FSN14288</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>07-05-2026_FNS14288</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -924,7 +918,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13320</t>
+          <t>04-05-2026_FNS13320</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -941,7 +935,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13319</t>
+          <t>04-05-2026_FNS13319</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -958,7 +952,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13321</t>
+          <t>04-05-2026_FNS13321</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -968,14 +962,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>p1902</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13402</t>
+          <t>04-05-2026_FNS13402</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -985,19 +979,19 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>p1892</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04-05-2026_FSN13400</t>
+          <t>04-05-2026_FNS13400</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 11-05-2026</t>
         </is>
       </c>
     </row>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="34668" yWindow="1764" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6216" yWindow="1476" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="20.77734375" customWidth="1" min="2" max="2"/>
     <col width="31.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="7.44140625" customWidth="1" min="4" max="4"/>
+    <col width="10.44140625" customWidth="1" min="4" max="4"/>
     <col width="73.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -547,6 +547,16 @@
           <t>allegato DDT 19-05-2026</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,15 +582,265 @@
           <t>18-05-2026_FNS16121</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P2274</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS56443</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>p2317</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS56468</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>p1756</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS16051</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P1752</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS16047</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>da consegnare grana padano 2 colli 16 buste</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P2316</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS56167</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>da consegnare 2 colli albicocca</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P1931</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS16097</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>da consegnare yogurt naturale BIO intero 3 cartoni 7 cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P1754</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS16049</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>da consegnare yogurt naturale BIO intero 8 cartoni 1 cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>p1853</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14-05-2026_FNS15693</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 5 cartoni 9 cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>p1855</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14-05-2026_FNS15694</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 8 cartoni</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>p1856</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14-05-2026_FNS15695</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 5 cartoni 1 cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>p1858</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14-05-2026_FNS15697</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 7 cartoni 4 cluster</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D1:D9 D21:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D1:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"parziale"</formula1>
     </dataValidation>
   </dataValidations>
@@ -594,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="B12:B109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -603,233 +863,6 @@
     <col width="27.5546875" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>P2274</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS56443</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Tutto il ddt</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>p2317</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS56468</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Tutto il ddt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>p1756</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS16051</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tutto il ddt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P1752</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS16047</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>da consegnare grana padano 2 colli 16 buste</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P2316</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS56167</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>da consegnare 2 colli albicocca</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P1931</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS16097</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>da consegnare yogurt naturale BIO intero 3 cartoni 7 cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P1754</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>18-05-2026_FNS16049</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>da consegnare yogurt naturale BIO intero 8 cartoni 1 cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>p1853</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>14-05-2026_FNS15693</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 5 cartoni 9 cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>p1855</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>14-05-2026_FNS15694</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 8 cartoni</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>p1856</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>14-05-2026_FNS15695</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 5 cartoni 1 cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>p1858</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>14-05-2026_FNS15697</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 7 cartoni 4 cluster</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="B12" s="1" t="n"/>
     </row>
@@ -1125,11 +1158,6 @@
       <c r="B109" s="1" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="D1:D11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"parziale"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -547,16 +547,6 @@
           <t>allegato DDT 19-05-2026</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>parziale</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Prova</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -569,7 +559,11 @@
           <t>18-05-2026_FNS56485</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>allegato DDT 19-05-2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -582,7 +576,11 @@
           <t>18-05-2026_FNS16121</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>allegato DDT 19-05-2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -837,6 +835,19 @@
           <t>da ritirare yogurt scaduto e da consegnare yogurt naturale BIO intero 7 cartoni 4 cluster</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>p2246</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19-05-2026_FNS57255</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -593,7 +593,6 @@
           <t>18-05-2026_FNS56443</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -611,7 +610,6 @@
           <t>18-05-2026_FNS56468</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -629,7 +627,6 @@
           <t>18-05-2026_FNS16051</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -647,7 +644,6 @@
           <t>18-05-2026_FNS16047</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -670,7 +666,6 @@
           <t>18-05-2026_FNS56167</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -693,7 +688,6 @@
           <t>18-05-2026_FNS16097</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -716,7 +710,6 @@
           <t>18-05-2026_FNS16049</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -741,7 +734,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 20-05-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -768,7 +761,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 20-05-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -795,7 +788,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 20-05-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -822,7 +815,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 20-05-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -847,7 +840,6 @@
           <t>19-05-2026_FNS57255</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -593,6 +593,7 @@
           <t>18-05-2026_FNS56443</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -610,6 +611,7 @@
           <t>18-05-2026_FNS56468</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -627,6 +629,7 @@
           <t>18-05-2026_FNS16051</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -644,6 +647,7 @@
           <t>18-05-2026_FNS16047</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -666,6 +670,7 @@
           <t>18-05-2026_FNS56167</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -688,6 +693,7 @@
           <t>18-05-2026_FNS16097</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -710,6 +716,7 @@
           <t>18-05-2026_FNS16049</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>parziale</t>
@@ -840,6 +847,7 @@
           <t>19-05-2026_FNS57255</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6216" yWindow="1476" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7920" yWindow="1644" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -848,6 +848,120 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>p1756</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13-04-2026_FNS9555</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da consegnare 1 collo di grana padano</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>p2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13-05-2026_FNS15487</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>p1850</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13-05-2026_FNS15450</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>p1791</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14-05-2026_FNS15670</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>allegato DDT 21-05-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>da consegnare Latte intero alta qualità (fardello da 12 bottiglie) 1 fardello e 5 bottiglie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>p8720</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>18-05-2026_FNS56989</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>da consegnare Mirtillo 1 collo e 4 porzioni</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 27-05-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 27-05-2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 27-05-2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1211,7 +1211,11 @@
           <t>25-05-2026_FNS59744</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -1229,7 +1233,11 @@
           <t>25-05-2026_FNS59743</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>In lavorazione</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1211,11 +1211,7 @@
           <t>25-05-2026_FNS59744</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -1233,12 +1229,53 @@
           <t>25-05-2026_FNS59743</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>In lavorazione</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>p2420</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>27-05-2026_FNS61281</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>allegato DDT 27-05-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>parziale</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Da consegnare solo "Mousse di nettarina biologica" 2 colli e due porzioni</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>p7732</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>26-05-2026_FNS60993</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
         </is>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="36060" yWindow="768" windowWidth="16860" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1211,7 +1211,11 @@
           <t>25-05-2026_FNS59744</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -1229,7 +1233,11 @@
           <t>25-05-2026_FNS59743</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
@@ -1249,7 +1257,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>allegato DDT 27-05-2026</t>
+          <t>in lavorazione</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1274,8 +1282,56 @@
           <t>26-05-2026_FNS60993</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P2286</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>26-05-2026_FNS60633</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tutto il ddt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>p1986</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>26-05-2026_FNS17353</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Tutto il ddt</t>
         </is>

--- a/AppLogSolutionLocale/dati/rientri_ddt.xlsx
+++ b/AppLogSolutionLocale/dati/rientri_ddt.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 28-05-2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 28-05-2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 28-05-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 28-05-2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 28-05-2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 28-05-2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
